--- a/Models/Верблюды/results/Верблюды - Результаты прогнозов Prophet.xlsx
+++ b/Models/Верблюды/results/Верблюды - Результаты прогнозов Prophet.xlsx
@@ -478,12 +478,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -668,12 +668,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -689,7 +689,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -744,12 +744,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -782,12 +782,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -820,12 +820,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -841,7 +841,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -858,31 +858,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.07</v>
+        <v>6.65</v>
       </c>
       <c r="E12" t="n">
-        <v>9.869999999999999</v>
+        <v>4.21</v>
       </c>
       <c r="F12" t="n">
-        <v>5.83</v>
+        <v>6.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[110.09, 68.64, 374.78]</t>
+          <t>[5.69, 48.73, 51.53]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[119.5, 72.6, 391.0]</t>
+          <t>[5.7, 49.87, 63.0]</t>
         </is>
       </c>
     </row>
@@ -894,31 +894,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.73</v>
+        <v>30.39</v>
       </c>
       <c r="E13" t="n">
-        <v>7.96</v>
+        <v>21.28</v>
       </c>
       <c r="F13" t="n">
-        <v>4.79</v>
+        <v>17.85</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[69.03, 378.63, 118.16]</t>
+          <t>[48.79, 51.6, 205.68]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[72.6, 391.0, 126.1]</t>
+          <t>[49.87, 63.0, 154.3]</t>
         </is>
       </c>
     </row>
@@ -930,31 +930,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.85</v>
+        <v>39.3</v>
       </c>
       <c r="E14" t="n">
-        <v>10.25</v>
+        <v>35.24</v>
       </c>
       <c r="F14" t="n">
-        <v>4.84</v>
+        <v>20.01</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[382.74, 118.87, 213.84]</t>
+          <t>[51.54, 206.91, 496.74]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[391.0, 126.1, 229.1]</t>
+          <t>[63.0, 154.3, 538.4]</t>
         </is>
       </c>
     </row>
@@ -966,31 +966,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.550000000000001</v>
+        <v>38.62</v>
       </c>
       <c r="E15" t="n">
-        <v>7.55</v>
+        <v>35.64</v>
       </c>
       <c r="F15" t="n">
-        <v>5.54</v>
+        <v>17.96</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[118.83, 214.26, 12.73]</t>
+          <t>[207.01, 500.63, 112.86]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[126.1, 229.1, 12.2]</t>
+          <t>[154.3, 538.4, 129.3]</t>
         </is>
       </c>
     </row>
@@ -1002,31 +1002,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.640000000000001</v>
+        <v>23.82</v>
       </c>
       <c r="E16" t="n">
-        <v>6.4</v>
+        <v>21.18</v>
       </c>
       <c r="F16" t="n">
-        <v>9.640000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[214.76, 12.81, 19.85]</t>
+          <t>[502.2, 112.62, 66.96]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[229.1, 12.2, 24.1]</t>
+          <t>[538.4, 129.3, 77.6]</t>
         </is>
       </c>
     </row>
@@ -1038,31 +1038,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.45</v>
+        <v>24.16</v>
       </c>
       <c r="E17" t="n">
-        <v>1.62</v>
+        <v>21.46</v>
       </c>
       <c r="F17" t="n">
-        <v>7.72</v>
+        <v>11.93</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[12.85, 19.91, 5.67]</t>
+          <t>[112.31, 66.95, 374.77]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[12.2, 24.1, 5.7]</t>
+          <t>[129.3, 77.6, 411.5]</t>
         </is>
       </c>
     </row>
@@ -1074,31 +1074,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.61</v>
+        <v>22.18</v>
       </c>
       <c r="E18" t="n">
-        <v>1.89</v>
+        <v>18.5</v>
       </c>
       <c r="F18" t="n">
-        <v>7.01</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[19.79, 5.67, 48.54]</t>
+          <t>[67.26, 375.7, 118.73]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[24.1, 5.7, 49.87]</t>
+          <t>[77.6, 411.5, 128.1]</t>
         </is>
       </c>
     </row>
@@ -1110,31 +1110,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.65</v>
+        <v>21.45</v>
       </c>
       <c r="E19" t="n">
-        <v>4.21</v>
+        <v>19.15</v>
       </c>
       <c r="F19" t="n">
-        <v>6.9</v>
+        <v>7.17</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[5.69, 48.73, 51.53]</t>
+          <t>[379.94, 120.08, 217.81]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[5.7, 49.87, 63.0]</t>
+          <t>[411.5, 128.1, 235.7]</t>
         </is>
       </c>
     </row>
@@ -1146,31 +1146,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.39</v>
+        <v>10.47</v>
       </c>
       <c r="E20" t="n">
-        <v>21.28</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>17.85</v>
+        <v>6.73</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[48.79, 51.6, 205.68]</t>
+          <t>[120.66, 219.18, 13.1]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[49.87, 63.0, 154.3]</t>
+          <t>[128.1, 235.7, 12.2]</t>
         </is>
       </c>
     </row>
@@ -1182,31 +1182,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>39.3</v>
+        <v>9.52</v>
       </c>
       <c r="E21" t="n">
-        <v>35.24</v>
+        <v>6.98</v>
       </c>
       <c r="F21" t="n">
-        <v>20.01</v>
+        <v>10.18</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[51.54, 206.91, 496.74]</t>
+          <t>[219.73, 13.14, 21.12]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[63.0, 154.3, 538.4]</t>
+          <t>[235.7, 12.2, 25.17]</t>
         </is>
       </c>
     </row>
@@ -1218,31 +1218,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>95.56</v>
+        <v>42.58</v>
       </c>
       <c r="E22" t="n">
-        <v>72.15000000000001</v>
+        <v>34.17</v>
       </c>
       <c r="F22" t="n">
-        <v>527.95</v>
+        <v>382.92</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[60.97, 32.42, 171.87]</t>
+          <t>[1.5, 77.12, 17.48]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[18.9, 17.4, 12.5]</t>
+          <t>[24.0, 7.7, 6.9]</t>
         </is>
       </c>
     </row>
@@ -1254,31 +1254,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>66.20999999999999</v>
+        <v>47.57</v>
       </c>
       <c r="E23" t="n">
-        <v>45.6</v>
+        <v>31.52</v>
       </c>
       <c r="F23" t="n">
-        <v>348.96</v>
+        <v>416.7</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[25.86, 125.88, 1.45]</t>
+          <t>[89.14, 19.38, 6.02]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[17.4, 12.5, 16.4]</t>
+          <t>[7.7, 6.9, 5.4]</t>
         </is>
       </c>
     </row>
@@ -1290,31 +1290,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66.89</v>
+        <v>48.1</v>
       </c>
       <c r="E24" t="n">
-        <v>45.77</v>
+        <v>30.06</v>
       </c>
       <c r="F24" t="n">
-        <v>358.09</v>
+        <v>256.21</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[127.11, 1.22, 4.08]</t>
+          <t>[12.31, 3.75, 95.72]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[12.5, 16.4, 11.6]</t>
+          <t>[6.9, 5.4, 12.6]</t>
         </is>
       </c>
     </row>
@@ -1326,31 +1326,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>44.78</v>
+        <v>47.37</v>
       </c>
       <c r="E25" t="n">
-        <v>32.87</v>
+        <v>32.95</v>
       </c>
       <c r="F25" t="n">
-        <v>204.12</v>
+        <v>248.82</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[1.13, 3.92, 92.35]</t>
+          <t>[3.49, 92.92, 39.22]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[16.4, 11.6, 16.7]</t>
+          <t>[5.4, 12.6, 22.6]</t>
         </is>
       </c>
     </row>
@@ -1362,31 +1362,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>51.28</v>
+        <v>41.57</v>
       </c>
       <c r="E26" t="n">
-        <v>39.87</v>
+        <v>27.98</v>
       </c>
       <c r="F26" t="n">
-        <v>248.49</v>
+        <v>207.06</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[4.74, 100.31, 44.85]</t>
+          <t>[83.56, 34.79, 18.22]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[11.6, 16.7, 15.7]</t>
+          <t>[12.6, 22.6, 19.0]</t>
         </is>
       </c>
     </row>
@@ -1398,31 +1398,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42.37</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>36.79</v>
+        <v>50.28</v>
       </c>
       <c r="F27" t="n">
-        <v>209.14</v>
+        <v>516.65</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[83.2, 36.81, 1.25]</t>
+          <t>[51.53, 28.35, 120.76]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[16.7, 15.7, 24.0]</t>
+          <t>[22.6, 19.0, 8.2]</t>
         </is>
       </c>
     </row>
@@ -1434,31 +1434,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>38.11</v>
+        <v>76.55</v>
       </c>
       <c r="E28" t="n">
-        <v>33.9</v>
+        <v>51.73</v>
       </c>
       <c r="F28" t="n">
-        <v>328.28</v>
+        <v>585.95</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[36.23, 1.32, 66.19]</t>
+          <t>[33.05, 139.68, 2.35]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[15.7, 24.0, 7.7]</t>
+          <t>[19.0, 8.2, 12.0]</t>
         </is>
       </c>
     </row>
@@ -1470,31 +1470,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>42.58</v>
+        <v>63.02</v>
       </c>
       <c r="E29" t="n">
-        <v>34.17</v>
+        <v>49.33</v>
       </c>
       <c r="F29" t="n">
-        <v>382.92</v>
+        <v>474.61</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[1.5, 77.12, 17.48]</t>
+          <t>[111.04, 2.02, 5.53]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[24.0, 7.7, 6.9]</t>
+          <t>[8.2, 12.0, 40.7]</t>
         </is>
       </c>
     </row>
@@ -1506,31 +1506,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47.57</v>
+        <v>32.85</v>
       </c>
       <c r="E30" t="n">
-        <v>31.52</v>
+        <v>29.84</v>
       </c>
       <c r="F30" t="n">
-        <v>416.7</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[89.14, 19.38, 6.02]</t>
+          <t>[1.31, 4.25, 83.96]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[7.7, 6.9, 5.4]</t>
+          <t>[12.0, 40.7, 41.6]</t>
         </is>
       </c>
     </row>
@@ -1542,31 +1542,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>48.1</v>
+        <v>34.94</v>
       </c>
       <c r="E31" t="n">
-        <v>30.06</v>
+        <v>31.73</v>
       </c>
       <c r="F31" t="n">
-        <v>256.21</v>
+        <v>81.59</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[12.31, 3.75, 95.72]</t>
+          <t>[5.1, 88.99, 40.29]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[6.9, 5.4, 12.6]</t>
+          <t>[40.7, 41.6, 28.1]</t>
         </is>
       </c>
     </row>
@@ -1578,31 +1578,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>133</v>
+        <v>120.73</v>
       </c>
       <c r="E32" t="n">
-        <v>132.3</v>
+        <v>109.47</v>
       </c>
       <c r="F32" t="n">
-        <v>33.69</v>
+        <v>23.11</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[442.31, 272.87, 569.41]</t>
+          <t>[172.28, 597.43, 552.96]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[323.81, 423.76, 441.9]</t>
+          <t>[133.5, 730.34, 709.68]</t>
         </is>
       </c>
     </row>
@@ -1614,31 +1614,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>110.67</v>
+        <v>120.23</v>
       </c>
       <c r="E33" t="n">
-        <v>95.90000000000001</v>
+        <v>104.77</v>
       </c>
       <c r="F33" t="n">
-        <v>23.78</v>
+        <v>14.95</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[272.12, 557.32, 239.75]</t>
+          <t>[601.56, 547.73, 561.18]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[423.76, 441.9, 219.1]</t>
+          <t>[730.34, 709.68, 537.6]</t>
         </is>
       </c>
     </row>
@@ -1650,31 +1650,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>107.63</v>
+        <v>472.75</v>
       </c>
       <c r="E34" t="n">
-        <v>96</v>
+        <v>330.13</v>
       </c>
       <c r="F34" t="n">
-        <v>23</v>
+        <v>37.98</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[580.44, 246.97, 609.29]</t>
+          <t>[547.64, 563.73, 1732.49]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[441.9, 219.1, 487.69]</t>
+          <t>[709.68, 537.6, 930.28]</t>
         </is>
       </c>
     </row>
@@ -1686,31 +1686,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>71.23</v>
+        <v>481.41</v>
       </c>
       <c r="E35" t="n">
-        <v>51.28</v>
+        <v>340.3</v>
       </c>
       <c r="F35" t="n">
-        <v>12.86</v>
+        <v>49.55</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[246.69, 607.79, 453.04]</t>
+          <t>[563.41, 1743.65, 503.8]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[219.1, 487.69, 446.9]</t>
+          <t>[537.6, 930.28, 322.1]</t>
         </is>
       </c>
     </row>
@@ -1722,31 +1722,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>81.11</v>
+        <v>481.34</v>
       </c>
       <c r="E36" t="n">
-        <v>66.56999999999999</v>
+        <v>334.78</v>
       </c>
       <c r="F36" t="n">
-        <v>21.39</v>
+        <v>49</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[607.65, 453.85, 118.64]</t>
+          <t>[1744.14, 502.68, 296.45]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[487.69, 446.9, 191.43]</t>
+          <t>[930.28, 322.1, 286.54]</t>
         </is>
       </c>
     </row>
@@ -1758,31 +1758,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>48.69</v>
+        <v>133.11</v>
       </c>
       <c r="E37" t="n">
-        <v>40.74</v>
+        <v>110.77</v>
       </c>
       <c r="F37" t="n">
-        <v>23.83</v>
+        <v>30.11</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[453.94, 119.19, 176.44]</t>
+          <t>[496.42, 293.82, 598.1]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[446.9, 191.43, 133.5]</t>
+          <t>[322.1, 286.54, 447.4]</t>
         </is>
       </c>
     </row>
@@ -1794,31 +1794,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>84.55</v>
+        <v>81.5</v>
       </c>
       <c r="E38" t="n">
-        <v>78.36</v>
+        <v>52.75</v>
       </c>
       <c r="F38" t="n">
-        <v>28.76</v>
+        <v>12.64</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[118.35, 175.86, 610.71]</t>
+          <t>[291.69, 587.91, 254.19]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[191.43, 133.5, 730.34]</t>
+          <t>[286.54, 447.4, 266.8]</t>
         </is>
       </c>
     </row>
@@ -1830,31 +1830,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>120.73</v>
+        <v>104.96</v>
       </c>
       <c r="E39" t="n">
-        <v>109.47</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>23.11</v>
+        <v>19.55</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[172.28, 597.43, 552.96]</t>
+          <t>[591.16, 255.58, 607.28]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[133.5, 730.34, 709.68]</t>
+          <t>[447.4, 266.8, 496.55]</t>
         </is>
       </c>
     </row>
@@ -1866,31 +1866,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>120.23</v>
+        <v>136.95</v>
       </c>
       <c r="E40" t="n">
-        <v>104.77</v>
+        <v>110.28</v>
       </c>
       <c r="F40" t="n">
-        <v>14.95</v>
+        <v>19.01</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[601.56, 547.73, 561.18]</t>
+          <t>[253.56, 602.17, 476.01]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[730.34, 709.68, 537.6]</t>
+          <t>[266.8, 496.55, 688.0]</t>
         </is>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>472.75</v>
+        <v>142.92</v>
       </c>
       <c r="E41" t="n">
-        <v>330.13</v>
+        <v>129.32</v>
       </c>
       <c r="F41" t="n">
-        <v>37.98</v>
+        <v>28.36</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[547.64, 563.73, 1732.49]</t>
+          <t>[601.23, 474.97, 142.43]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[709.68, 537.6, 930.28]</t>
+          <t>[496.55, 688.0, 212.7]</t>
         </is>
       </c>
     </row>
@@ -1938,19 +1938,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -1976,19 +1976,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="E43" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.01]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.8]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2014,19 +2014,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="E44" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.02]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[0.0, 0.8, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2052,19 +2052,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="E45" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.05, 0.19, 0.0]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[0.8, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2090,19 +2090,19 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.02, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.5]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -2128,19 +2128,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.29</v>
+        <v>0.4</v>
       </c>
       <c r="E47" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[0.0, 0.5, 0.0]</t>
+          <t>[0.0, 0.7, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2166,19 +2166,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.29</v>
+        <v>1.72</v>
       </c>
       <c r="E48" t="n">
-        <v>0.17</v>
+        <v>1.2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[0.5, 0.0, 0.0]</t>
+          <t>[0.7, 0.0, 2.9]</t>
         </is>
       </c>
     </row>
@@ -2204,19 +2204,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.23</v>
+        <v>1.75</v>
       </c>
       <c r="E49" t="n">
-        <v>0.13</v>
+        <v>1.27</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 2.9, 0.9]</t>
         </is>
       </c>
     </row>
@@ -2242,19 +2242,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.23</v>
+        <v>1.75</v>
       </c>
       <c r="E50" t="n">
-        <v>0.14</v>
+        <v>1.27</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.01]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[2.9, 0.9, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2280,19 +2280,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="E51" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2301,12 +2301,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.02]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.9, 0.0, 0.6]</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2774,12 +2774,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3458,31 +3458,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.9</v>
+        <v>27.79</v>
       </c>
       <c r="E82" t="n">
-        <v>19.09</v>
+        <v>18.33</v>
       </c>
       <c r="F82" t="n">
-        <v>23.87</v>
+        <v>30.08</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[71.84, 35.4, 42.81]</t>
+          <t>[9.77, 50.65, 28.6]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[109.8, 32.3, 59.0]</t>
+          <t>[14.2, 98.5, 25.9]</t>
         </is>
       </c>
     </row>
@@ -3494,31 +3494,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>9.51</v>
+        <v>29.28</v>
       </c>
       <c r="E83" t="n">
-        <v>8.359999999999999</v>
+        <v>22.39</v>
       </c>
       <c r="F83" t="n">
-        <v>26.05</v>
+        <v>36.17</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[35.61, 44.7, 24.57]</t>
+          <t>[50.64, 28.66, 50.16]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[32.3, 59.0, 17.1]</t>
+          <t>[98.5, 25.9, 33.6]</t>
         </is>
       </c>
     </row>
@@ -3530,31 +3530,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9.94</v>
+        <v>11.58</v>
       </c>
       <c r="E84" t="n">
-        <v>9.17</v>
+        <v>9.9</v>
       </c>
       <c r="F84" t="n">
-        <v>35.66</v>
+        <v>76.72</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[44.45, 24.08, 8.42]</t>
+          <t>[28.48, 50.93, 15.58]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[59.0, 17.1, 14.4]</t>
+          <t>[25.9, 33.6, 5.8]</t>
         </is>
       </c>
     </row>
@@ -3566,31 +3566,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6.12</v>
+        <v>27.98</v>
       </c>
       <c r="E85" t="n">
-        <v>6.01</v>
+        <v>23.42</v>
       </c>
       <c r="F85" t="n">
-        <v>34.86</v>
+        <v>81.84</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[24.46, 8.33, 19.13]</t>
+          <t>[50.19, 14.82, 65.16]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[17.1, 14.4, 23.74]</t>
+          <t>[33.6, 5.8, 109.8]</t>
         </is>
       </c>
     </row>
@@ -3602,31 +3602,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4.84</v>
+        <v>25.7</v>
       </c>
       <c r="E86" t="n">
-        <v>4.73</v>
+        <v>18.32</v>
       </c>
       <c r="F86" t="n">
-        <v>28.57</v>
+        <v>65.87</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[8.4, 19.01, 17.75]</t>
+          <t>[14.54, 66.23, 39.06]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[14.4, 23.74, 14.3]</t>
+          <t>[5.8, 109.8, 36.4]</t>
         </is>
       </c>
     </row>
@@ -3638,31 +3638,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4.26</v>
+        <v>27.33</v>
       </c>
       <c r="E87" t="n">
-        <v>4.22</v>
+        <v>20.17</v>
       </c>
       <c r="F87" t="n">
-        <v>25.23</v>
+        <v>23.23</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[19.01, 17.81, 9.77]</t>
+          <t>[63.97, 39.71, 49.01]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[23.74, 14.3, 14.2]</t>
+          <t>[109.8, 36.4, 60.4]</t>
         </is>
       </c>
     </row>
@@ -3674,31 +3674,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>27.74</v>
+        <v>6.6</v>
       </c>
       <c r="E88" t="n">
-        <v>18.52</v>
+        <v>5.13</v>
       </c>
       <c r="F88" t="n">
-        <v>34.51</v>
+        <v>13.93</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[17.7, 9.75, 50.78]</t>
+          <t>[37.09, 49.74, 22.25]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[14.3, 14.2, 98.5]</t>
+          <t>[36.4, 60.4, 18.2]</t>
         </is>
       </c>
     </row>
@@ -3710,31 +3710,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>27.79</v>
+        <v>7.56</v>
       </c>
       <c r="E89" t="n">
-        <v>18.33</v>
+        <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>30.08</v>
+        <v>26.42</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[9.77, 50.65, 28.6]</t>
+          <t>[49.53, 22.25, 9.52]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[14.2, 98.5, 25.9]</t>
+          <t>[60.4, 18.2, 15.6]</t>
         </is>
       </c>
     </row>
@@ -3746,31 +3746,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>29.28</v>
+        <v>4.25</v>
       </c>
       <c r="E90" t="n">
-        <v>22.39</v>
+        <v>3.56</v>
       </c>
       <c r="F90" t="n">
-        <v>36.17</v>
+        <v>21.34</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[50.64, 28.66, 50.16]</t>
+          <t>[22.43, 9.59, 19.26]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[98.5, 25.9, 33.6]</t>
+          <t>[18.2, 15.6, 19.7]</t>
         </is>
       </c>
     </row>
@@ -3782,31 +3782,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.58</v>
+        <v>3.86</v>
       </c>
       <c r="E91" t="n">
-        <v>9.9</v>
+        <v>3.1</v>
       </c>
       <c r="F91" t="n">
-        <v>76.72</v>
+        <v>20.17</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[28.48, 50.93, 15.58]</t>
+          <t>[9.47, 19.17, 16.83]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[25.9, 33.6, 5.8]</t>
+          <t>[15.6, 19.7, 14.2]</t>
         </is>
       </c>
     </row>
@@ -3818,31 +3818,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>7.22</v>
       </c>
       <c r="E92" t="n">
-        <v>1.98</v>
+        <v>7.11</v>
       </c>
       <c r="F92" t="n">
-        <v>74.61</v>
+        <v>56.09</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[7.56, 8.28, 9.87]</t>
+          <t>[0.79, 22.85, 6.23]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[2.4, 8.7, 9.5]</t>
+          <t>[6.4, 31.5, 13.3]</t>
         </is>
       </c>
     </row>
@@ -3854,31 +3854,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.22</v>
+        <v>7.43</v>
       </c>
       <c r="E93" t="n">
-        <v>1.12</v>
+        <v>6.36</v>
       </c>
       <c r="F93" t="n">
-        <v>21.3</v>
+        <v>45.34</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[7.01, 8.34, 2.12]</t>
+          <t>[21.04, 5.91, 3.83]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[8.7, 9.5, 1.6]</t>
+          <t>[31.5, 13.3, 2.6]</t>
         </is>
       </c>
     </row>
@@ -3890,31 +3890,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1.58</v>
+        <v>4.65</v>
       </c>
       <c r="E94" t="n">
-        <v>1.36</v>
+        <v>4.12</v>
       </c>
       <c r="F94" t="n">
-        <v>22.1</v>
+        <v>44.39</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[8.23, 2.04, 11.68]</t>
+          <t>[6.45, 4.17, 22.34]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[9.5, 1.6, 9.3]</t>
+          <t>[13.3, 2.6, 18.4]</t>
         </is>
       </c>
     </row>
@@ -3926,31 +3926,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7.06</v>
+        <v>4.4</v>
       </c>
       <c r="E95" t="n">
-        <v>5.08</v>
+        <v>4.11</v>
       </c>
       <c r="F95" t="n">
-        <v>27.78</v>
+        <v>98.14</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[2.12, 12.13, 69.89]</t>
+          <t>[4.54, 24.07, 7.22]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[1.6, 9.3, 58.0]</t>
+          <t>[2.6, 18.4, 2.5]</t>
         </is>
       </c>
     </row>
@@ -3962,31 +3962,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5.78</v>
+        <v>2.87</v>
       </c>
       <c r="E96" t="n">
-        <v>4.24</v>
+        <v>2.63</v>
       </c>
       <c r="F96" t="n">
-        <v>54.75</v>
+        <v>59.65</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[11.55, 67.73, 1.34]</t>
+          <t>[21.47, 6.25, 7.64]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[9.3, 58.0, 0.6]</t>
+          <t>[18.4, 2.5, 8.7]</t>
         </is>
       </c>
     </row>
@@ -3998,31 +3998,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>7.56</v>
+        <v>2.58</v>
       </c>
       <c r="E97" t="n">
-        <v>6.04</v>
+        <v>1.63</v>
       </c>
       <c r="F97" t="n">
-        <v>77.27</v>
+        <v>61.07</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[69.83, 1.35, 0.86]</t>
+          <t>[6.96, 8.42, 9.86]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[58.0, 0.6, 6.4]</t>
+          <t>[2.5, 8.7, 9.7]</t>
         </is>
       </c>
     </row>
@@ -4034,31 +4034,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5.75</v>
+        <v>0.98</v>
       </c>
       <c r="E98" t="n">
-        <v>4.87</v>
+        <v>0.9</v>
       </c>
       <c r="F98" t="n">
-        <v>84.26000000000001</v>
+        <v>16.09</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[1.44, 0.87, 23.26]</t>
+          <t>[7.42, 8.67, 2.09]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[0.6, 6.4, 31.5]</t>
+          <t>[8.7, 9.7, 1.7]</t>
         </is>
       </c>
     </row>
@@ -4070,31 +4070,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7.22</v>
+        <v>1.6</v>
       </c>
       <c r="E99" t="n">
-        <v>7.11</v>
+        <v>1.33</v>
       </c>
       <c r="F99" t="n">
-        <v>56.09</v>
+        <v>19.74</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[0.79, 22.85, 6.23]</t>
+          <t>[8.6, 2.07, 12.13]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[6.4, 31.5, 13.3]</t>
+          <t>[9.7, 1.7, 9.6]</t>
         </is>
       </c>
     </row>
@@ -4106,31 +4106,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>7.43</v>
+        <v>5.2</v>
       </c>
       <c r="E100" t="n">
-        <v>6.36</v>
+        <v>3.88</v>
       </c>
       <c r="F100" t="n">
-        <v>45.34</v>
+        <v>21.77</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[21.04, 5.91, 3.83]</t>
+          <t>[2.1, 12.22, 68.53]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[31.5, 13.3, 2.6]</t>
+          <t>[1.7, 9.6, 59.92]</t>
         </is>
       </c>
     </row>
@@ -4142,31 +4142,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>4.65</v>
+        <v>4.94</v>
       </c>
       <c r="E101" t="n">
-        <v>4.12</v>
+        <v>3.74</v>
       </c>
       <c r="F101" t="n">
-        <v>44.39</v>
+        <v>48.14</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[6.45, 4.17, 22.34]</t>
+          <t>[12.02, 68.1, 1.23]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[13.3, 2.6, 18.4]</t>
+          <t>[9.6, 59.92, 0.6]</t>
         </is>
       </c>
     </row>
@@ -4178,19 +4178,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5.69</v>
+        <v>4.99</v>
       </c>
       <c r="E102" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[0.06, 0.01, 0.79]</t>
+          <t>[0.0, 0.56, 0.01]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[0.9, 0.0, 10.6]</t>
+          <t>[0.0, 9.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4216,19 +4216,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>5.72</v>
+        <v>5.04</v>
       </c>
       <c r="E103" t="n">
-        <v>3.81</v>
+        <v>2.97</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[0.01, 0.83, 0.33]</t>
+          <t>[0.47, 0.01, 0.18]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[0.0, 10.6, 2.0]</t>
+          <t>[9.2, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4254,31 +4254,33 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>6.78</v>
+        <v>1.52</v>
       </c>
       <c r="E104" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="F104" t="n">
-        <v>92.63</v>
+        <v>0.95</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[0.55, 0.22, 0.38]</t>
+          <t>[0.01, 0.21, 2.62]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[10.6, 2.0, 6.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4290,31 +4292,33 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5.37</v>
+        <v>1.09</v>
       </c>
       <c r="E105" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="F105" t="n">
-        <v>90.33</v>
+        <v>0.79</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[0.28, 0.49, 0.56]</t>
+          <t>[0.15, 1.85, 0.04]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[2.0, 6.2, 7.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -4326,19 +4330,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>5.1</v>
+        <v>1.06</v>
       </c>
       <c r="E106" t="n">
-        <v>4.14</v>
+        <v>0.72</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4347,12 +4351,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[0.69, 0.8, 0.0]</t>
+          <t>[1.8, 0.04, 0.0]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[6.2, 7.7, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4364,19 +4368,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4.1</v>
+        <v>5.54</v>
       </c>
       <c r="E107" t="n">
-        <v>2.37</v>
+        <v>3.32</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4385,12 +4389,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[0.59, 0.0, 0.0]</t>
+          <t>[0.02, 0.0, 0.22]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[7.7, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 9.8]</t>
         </is>
       </c>
     </row>
@@ -4402,19 +4406,19 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4.88</v>
+        <v>5.55</v>
       </c>
       <c r="E108" t="n">
-        <v>2.82</v>
+        <v>3.77</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4423,12 +4427,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.75]</t>
+          <t>[0.0, 0.37, 0.13]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 9.2]</t>
+          <t>[0.0, 9.8, 2.0]</t>
         </is>
       </c>
     </row>
@@ -4440,33 +4444,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>4.99</v>
+        <v>6.69</v>
       </c>
       <c r="E109" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>5.91</v>
+      </c>
+      <c r="F109" t="n">
+        <v>97.56999999999999</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[0.0, 0.56, 0.01]</t>
+          <t>[0.19, 0.07, 0.12]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[0.0, 9.2, 0.0]</t>
+          <t>[9.8, 2.0, 6.3]</t>
         </is>
       </c>
     </row>
@@ -4478,33 +4480,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5.04</v>
+        <v>5.14</v>
       </c>
       <c r="E110" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>4.73</v>
+      </c>
+      <c r="F110" t="n">
+        <v>96</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[0.47, 0.01, 0.18]</t>
+          <t>[0.11, 0.2, 0.21]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[9.2, 0.0, 0.0]</t>
+          <t>[2.0, 6.3, 6.4]</t>
         </is>
       </c>
     </row>
@@ -4516,19 +4516,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.52</v>
+        <v>5</v>
       </c>
       <c r="E111" t="n">
-        <v>0.95</v>
+        <v>4.08</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4537,12 +4537,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[0.01, 0.21, 2.62]</t>
+          <t>[0.22, 0.24, -0.0]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.3, 6.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.2]</t>
         </is>
       </c>
     </row>
@@ -4668,19 +4668,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4706,19 +4706,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.2, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4820,12 +4820,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4896,19 +4896,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -4934,31 +4934,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1966.26</v>
+        <v>45.89</v>
       </c>
       <c r="E122" t="n">
-        <v>1961.1</v>
+        <v>28.98</v>
       </c>
       <c r="F122" t="n">
-        <v>560.79</v>
+        <v>120.47</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[2427.06, 2394.23, 2114.42]</t>
+          <t>[0.49, 0.99, 120.4]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[369.4, 328.32, 354.71]</t>
+          <t>[3.82, 5.31, 41.1]</t>
         </is>
       </c>
     </row>
@@ -4970,31 +4970,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1925.03</v>
+        <v>1276.21</v>
       </c>
       <c r="E123" t="n">
-        <v>1607.13</v>
+        <v>770.22</v>
       </c>
       <c r="F123" t="n">
-        <v>3328.53</v>
+        <v>272.59</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[2842.04, 2541.93, 121.85]</t>
+          <t>[1.18, 139.37, 2649.11]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[328.32, 354.71, 1.4]</t>
+          <t>[5.31, 41.1, 440.84]</t>
         </is>
       </c>
     </row>
@@ -5006,31 +5006,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1072.51</v>
+        <v>1314.63</v>
       </c>
       <c r="E124" t="n">
-        <v>658.23</v>
+        <v>1094.57</v>
       </c>
       <c r="F124" t="n">
-        <v>3258.24</v>
+        <v>203.55</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[2209.39, 104.79, 17.5]</t>
+          <t>[107.35, 2002.99, 3396.08]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[354.71, 1.4, 0.89]</t>
+          <t>[41.1, 440.84, 1740.77]</t>
         </is>
       </c>
     </row>
@@ -5042,31 +5042,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>48.29</v>
+        <v>1922.58</v>
       </c>
       <c r="E125" t="n">
-        <v>32.47</v>
+        <v>1916.97</v>
       </c>
       <c r="F125" t="n">
-        <v>2469.62</v>
+        <v>313.03</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[84.06, 13.44, 0.13]</t>
+          <t>[2188.09, 3846.06, 2348.44]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[1.4, 0.89, 2.32]</t>
+          <t>[440.84, 1740.77, 450.07]</t>
         </is>
       </c>
     </row>
@@ -5078,31 +5078,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5.81</v>
+        <v>2597.03</v>
       </c>
       <c r="E126" t="n">
-        <v>4.12</v>
+        <v>2586.6</v>
       </c>
       <c r="F126" t="n">
-        <v>404.99</v>
+        <v>450.32</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[10.69, 0.09, 1.57]</t>
+          <t>[4609.85, 3041.15, 2676.37]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[0.89, 2.32, 1.9]</t>
+          <t>[1740.77, 450.07, 376.72]</t>
         </is>
       </c>
     </row>
@@ -5114,31 +5114,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2.3</v>
+        <v>1744.79</v>
       </c>
       <c r="E127" t="n">
-        <v>1.86</v>
+        <v>1740.97</v>
       </c>
       <c r="F127" t="n">
-        <v>61.36</v>
+        <v>456.68</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[0.1, 1.87, 0.5]</t>
+          <t>[2234.35, 1959.7, 2190.96]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[2.32, 1.9, 3.82]</t>
+          <t>[450.07, 376.72, 335.32]</t>
         </is>
       </c>
     </row>
@@ -5150,31 +5150,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3.15</v>
+        <v>1495.97</v>
       </c>
       <c r="E128" t="n">
-        <v>2.57</v>
+        <v>1224.16</v>
       </c>
       <c r="F128" t="n">
-        <v>57.19</v>
+        <v>349.79</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[1.84, 0.5, 0.98]</t>
+          <t>[2136.92, 2236.73, 83.08]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[1.9, 3.82, 5.31]</t>
+          <t>[376.72, 335.32, 72.2]</t>
         </is>
       </c>
     </row>
@@ -5186,31 +5186,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>45.89</v>
+        <v>760.96</v>
       </c>
       <c r="E129" t="n">
-        <v>28.98</v>
+        <v>446.56</v>
       </c>
       <c r="F129" t="n">
-        <v>120.47</v>
+        <v>341.18</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[0.49, 0.99, 120.4]</t>
+          <t>[1653.24, 59.71, 10.77]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[3.82, 5.31, 41.1]</t>
+          <t>[335.32, 72.2, 1.51]</t>
         </is>
       </c>
     </row>
@@ -5222,31 +5222,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1276.21</v>
+        <v>33.61</v>
       </c>
       <c r="E130" t="n">
-        <v>770.22</v>
+        <v>24.99</v>
       </c>
       <c r="F130" t="n">
-        <v>272.59</v>
+        <v>265.92</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[1.18, 139.37, 2649.11]</t>
+          <t>[64.34, 11.89, 0.2]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[5.31, 41.1, 440.84]</t>
+          <t>[72.2, 1.51, 56.94]</t>
         </is>
       </c>
     </row>
@@ -5258,31 +5258,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1314.63</v>
+        <v>33.95</v>
       </c>
       <c r="E131" t="n">
-        <v>1094.57</v>
+        <v>26.17</v>
       </c>
       <c r="F131" t="n">
-        <v>203.55</v>
+        <v>295.3</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[107.35, 2002.99, 3396.08]</t>
+          <t>[12.14, 0.2, 2.44]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[41.1, 440.84, 1740.77]</t>
+          <t>[1.51, 56.94, 13.58]</t>
         </is>
       </c>
     </row>
@@ -5294,31 +5294,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>40.43</v>
+        <v>187.34</v>
       </c>
       <c r="E132" t="n">
-        <v>36.42</v>
+        <v>167.06</v>
       </c>
       <c r="F132" t="n">
-        <v>27.89</v>
+        <v>33.1</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[194.97, 243.41, 23.59]</t>
+          <t>[170.52, 687.2, 327.4]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[168.4, 304.5, 45.2]</t>
+          <t>[409.3, 901.6, 279.4]</t>
         </is>
       </c>
     </row>
@@ -5330,31 +5330,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>114.34</v>
+        <v>123.41</v>
       </c>
       <c r="E133" t="n">
-        <v>86.73999999999999</v>
+        <v>95.83</v>
       </c>
       <c r="F133" t="n">
-        <v>38.76</v>
+        <v>16.76</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[254.07, 25.95, 142.96]</t>
+          <t>[695.98, 325.73, 361.75]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[304.5, 45.2, 333.5]</t>
+          <t>[901.6, 279.4, 326.2]</t>
         </is>
       </c>
     </row>
@@ -5366,31 +5366,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>105.82</v>
+        <v>245.4</v>
       </c>
       <c r="E134" t="n">
-        <v>76.04000000000001</v>
+        <v>170.4</v>
       </c>
       <c r="F134" t="n">
-        <v>39.61</v>
+        <v>25.55</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[24.35, 153.44, 172.51]</t>
+          <t>[338.53, 358.63, 501.74]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[45.2, 333.5, 145.3]</t>
+          <t>[279.4, 326.2, 921.4]</t>
         </is>
       </c>
     </row>
@@ -5402,31 +5402,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>117.33</v>
+        <v>251.94</v>
       </c>
       <c r="E135" t="n">
-        <v>97.11</v>
+        <v>172.09</v>
       </c>
       <c r="F135" t="n">
-        <v>33.22</v>
+        <v>30.36</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[147.59, 173.72, 239.01]</t>
+          <t>[350.74, 489.89, 224.22]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[333.5, 145.3, 316.0]</t>
+          <t>[326.2, 921.4, 164.0]</t>
         </is>
       </c>
     </row>
@@ -5438,31 +5438,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>45.46</v>
+        <v>274.47</v>
       </c>
       <c r="E136" t="n">
-        <v>39.47</v>
+        <v>232.61</v>
       </c>
       <c r="F136" t="n">
-        <v>17.85</v>
+        <v>40.53</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[173.64, 245.08, 184.36]</t>
+          <t>[501.73, 228.3, 366.62]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[145.3, 316.0, 165.2]</t>
+          <t>[921.4, 164.0, 580.5]</t>
         </is>
       </c>
     </row>
@@ -5474,31 +5474,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>143.48</v>
+        <v>133.82</v>
       </c>
       <c r="E137" t="n">
-        <v>107.36</v>
+        <v>115.57</v>
       </c>
       <c r="F137" t="n">
-        <v>29.66</v>
+        <v>46.84</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[246.96, 179.94, 171.02]</t>
+          <t>[229.17, 369.58, 38.96]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[316.0, 165.2, 409.3]</t>
+          <t>[164.0, 580.5, 109.58]</t>
         </is>
       </c>
     </row>
@@ -5510,31 +5510,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>180.66</v>
+        <v>137.51</v>
       </c>
       <c r="E138" t="n">
-        <v>153.4</v>
+        <v>117.05</v>
       </c>
       <c r="F138" t="n">
-        <v>30.67</v>
+        <v>55.69</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[184.69, 174.4, 695.78]</t>
+          <t>[361.56, 38.16, 155.49]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[165.2, 409.3, 901.6]</t>
+          <t>[580.5, 109.58, 94.7]</t>
         </is>
       </c>
     </row>
@@ -5546,31 +5546,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>187.34</v>
+        <v>53.84</v>
       </c>
       <c r="E139" t="n">
-        <v>167.06</v>
+        <v>47.03</v>
       </c>
       <c r="F139" t="n">
-        <v>33.1</v>
+        <v>44.6</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[170.52, 687.2, 327.4]</t>
+          <t>[38.96, 154.7, 184.93]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[409.3, 901.6, 279.4]</t>
+          <t>[109.58, 94.7, 174.45]</t>
         </is>
       </c>
     </row>
@@ -5582,31 +5582,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>123.41</v>
+        <v>42.38</v>
       </c>
       <c r="E140" t="n">
-        <v>95.83</v>
+        <v>34.57</v>
       </c>
       <c r="F140" t="n">
-        <v>16.76</v>
+        <v>29.83</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[695.98, 325.73, 361.75]</t>
+          <t>[163.36, 197.48, 329.87]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[901.6, 279.4, 326.2]</t>
+          <t>[94.7, 174.45, 317.85]</t>
         </is>
       </c>
     </row>
@@ -5618,31 +5618,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>245.4</v>
+        <v>17.37</v>
       </c>
       <c r="E141" t="n">
-        <v>170.4</v>
+        <v>14.47</v>
       </c>
       <c r="F141" t="n">
-        <v>25.55</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[338.53, 358.63, 501.74]</t>
+          <t>[191.27, 319.55, 188.69]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[279.4, 326.2, 921.4]</t>
+          <t>[174.45, 317.85, 163.8]</t>
         </is>
       </c>
     </row>
@@ -5654,19 +5654,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5675,12 +5675,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
     </row>
@@ -5692,19 +5692,19 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>81292777.40000001</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>46934407.15</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5713,12 +5713,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, 140803222.15]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.7, 1.4]</t>
         </is>
       </c>
     </row>
@@ -5730,33 +5730,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>6739110.96</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>3890833.45</v>
+      </c>
+      <c r="F144" t="n">
+        <v>277916318.45</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 11672483.98, 0.03]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.7, 1.4, 17.1]</t>
         </is>
       </c>
     </row>
@@ -5768,33 +5766,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.97</v>
+        <v>20.65</v>
       </c>
       <c r="E145" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>17.78</v>
+      </c>
+      <c r="F145" t="n">
+        <v>804.21</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[32.38, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.68]</t>
+          <t>[1.4, 17.1, 5.25]</t>
         </is>
       </c>
     </row>
@@ -5806,33 +5802,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.97</v>
+        <v>10.36</v>
       </c>
       <c r="E146" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>7.92</v>
+      </c>
+      <c r="F146" t="n">
+        <v>100</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[0.0, 1.68, 0.0]</t>
+          <t>[17.1, 5.25, 1.4]</t>
         </is>
       </c>
     </row>
@@ -5844,19 +5838,19 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.97</v>
+        <v>3.14</v>
       </c>
       <c r="E147" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -5865,12 +5859,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[1.68, 0.0, 0.0]</t>
+          <t>[5.25, 1.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5882,19 +5876,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -5903,12 +5897,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.4, 0.0, 0.35]</t>
         </is>
       </c>
     </row>
@@ -5920,19 +5914,19 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E149" t="n">
-        <v>0.23</v>
+        <v>0.12</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5941,12 +5935,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.0, 0.35, 0.0]</t>
         </is>
       </c>
     </row>
@@ -5958,19 +5952,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>81292777.40000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="E150" t="n">
-        <v>46934407.15</v>
+        <v>55.46</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -5979,12 +5973,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 140803222.15]</t>
+          <t>[0.0, 0.0, 170.0]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.4]</t>
+          <t>[0.35, 0.0, 3.98]</t>
         </is>
       </c>
     </row>
@@ -5996,31 +5990,33 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6739110.96</v>
+        <v>209.7</v>
       </c>
       <c r="E151" t="n">
-        <v>3890833.45</v>
-      </c>
-      <c r="F151" t="n">
-        <v>277916318.45</v>
+        <v>121.07</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[-0.0, 11672483.98, 0.03]</t>
+          <t>[0.0, 367.18, 0.0]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[0.7, 1.4, 17.1]</t>
+          <t>[0.0, 3.98, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6032,19 +6028,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>7.31</v>
+        <v>725334139.3200001</v>
       </c>
       <c r="E152" t="n">
-        <v>4.31</v>
+        <v>418771870.71</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -6053,12 +6049,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[0.07, 0.1, 0.14]</t>
+          <t>[-0.0, 1256315582.97, 26.06]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[0.0, 0.3, 12.8]</t>
+          <t>[4.3, 1.2, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6070,19 +6066,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>7.39</v>
+        <v>8484018.75</v>
       </c>
       <c r="E153" t="n">
-        <v>4.36</v>
+        <v>4898251.97</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -6091,12 +6087,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[0.01, 0.01, 0.01]</t>
+          <t>[14694752.72, 1.69, -0.0]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[0.3, 12.8, 0.0]</t>
+          <t>[1.2, 0.0, 2.7]</t>
         </is>
       </c>
     </row>
@@ -6108,19 +6104,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>7.38</v>
+        <v>165203.55</v>
       </c>
       <c r="E154" t="n">
-        <v>4.28</v>
+        <v>95441.55</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -6129,12 +6125,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[0.02, 0.03, 0.04]</t>
+          <t>[181.06, -0.0, 286142.78]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[12.8, 0.0, 0.0]</t>
+          <t>[0.0, 2.7, 1.9]</t>
         </is>
       </c>
     </row>
@@ -6146,19 +6142,19 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>21.73</v>
+        <v>6631034.73</v>
       </c>
       <c r="E155" t="n">
-        <v>12.62</v>
+        <v>3828430.59</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -6167,12 +6163,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[0.09, 0.12, 0.16]</t>
+          <t>[-0.0, 11485290.96, 0.0]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 37.8]</t>
+          <t>[2.7, 1.9, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6184,19 +6180,19 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>21.81</v>
+        <v>388.89</v>
       </c>
       <c r="E156" t="n">
-        <v>12.61</v>
+        <v>242.04</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -6205,12 +6201,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[0.02, 0.02, 0.02]</t>
+          <t>[673.24, 0.0, 55.18]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[0.0, 37.8, 0.0]</t>
+          <t>[1.9, 0.0, 0.4]</t>
         </is>
       </c>
     </row>
@@ -6222,19 +6218,19 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>21.96</v>
+        <v>149.09</v>
       </c>
       <c r="E157" t="n">
-        <v>14.03</v>
+        <v>106.75</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -6243,12 +6239,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 72.76, 248.99]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[37.8, 0.0, 4.3]</t>
+          <t>[0.0, 0.4, 1.1]</t>
         </is>
       </c>
     </row>
@@ -6260,19 +6256,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>90975260.09</v>
+        <v>550.08</v>
       </c>
       <c r="E158" t="n">
-        <v>52525962.34</v>
+        <v>379.43</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -6281,12 +6277,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[4110.07, -0.0, 157573773.85]</t>
+          <t>[930.03, 209.76, 0.0]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[0.0, 4.3, 1.2]</t>
+          <t>[0.4, 1.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6298,19 +6294,19 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>725334139.3200001</v>
+        <v>98.78</v>
       </c>
       <c r="E159" t="n">
-        <v>418771870.71</v>
+        <v>57.03</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -6319,12 +6315,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[-0.0, 1256315582.97, 26.06]</t>
+          <t>[172.19, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[4.3, 1.2, 0.0]</t>
+          <t>[1.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6336,19 +6332,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>8484018.75</v>
+        <v>100.18</v>
       </c>
       <c r="E160" t="n">
-        <v>4898251.97</v>
+        <v>57.84</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -6357,12 +6353,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[14694752.72, 1.69, -0.0]</t>
+          <t>[0.0, 0.0, 201.82]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[1.2, 0.0, 2.7]</t>
+          <t>[0.0, 0.0, 28.3]</t>
         </is>
       </c>
     </row>
@@ -6374,19 +6370,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>165203.55</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>95441.55</v>
+        <v>49.28</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -6395,12 +6391,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[181.06, -0.0, 286142.78]</t>
+          <t>[0.0, 176.14, 0.0]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[0.0, 2.7, 1.9]</t>
+          <t>[0.0, 28.3, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6408,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6450,12 +6446,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6488,19 +6484,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>2136145.89</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>1233304.4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -6509,7 +6505,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 3699913.21]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6526,19 +6522,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>310321.32</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>179164.1</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -6547,7 +6543,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 537492.29, -0.0]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6564,19 +6560,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>525.66</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>303.49</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -6585,7 +6581,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[910.47, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6602,12 +6598,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6640,12 +6636,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6678,12 +6674,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6716,12 +6712,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6754,19 +6750,19 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2136145.89</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>1233304.4</v>
+        <v>0</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -6775,7 +6771,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 3699913.21]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6792,19 +6788,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="E172" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6813,12 +6809,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[0.0, 0.42, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6830,19 +6826,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -6851,12 +6847,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[0.42, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6864,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6889,7 +6885,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6906,12 +6902,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6927,7 +6923,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -6944,12 +6940,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6965,7 +6961,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -6982,19 +6978,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -7003,12 +6999,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7020,19 +7016,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -7041,12 +7037,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7058,19 +7054,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -7084,7 +7080,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -7096,12 +7092,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -7117,7 +7113,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7134,12 +7130,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -7155,7 +7151,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7172,12 +7168,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7210,12 +7206,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -7248,12 +7244,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7286,12 +7282,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -7324,12 +7320,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -7362,12 +7358,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -7400,12 +7396,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7438,12 +7434,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7476,12 +7472,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7514,12 +7510,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7552,31 +7548,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11.43</v>
+        <v>41.49</v>
       </c>
       <c r="E192" t="n">
-        <v>10.99</v>
+        <v>38.34</v>
       </c>
       <c r="F192" t="n">
-        <v>15.59</v>
+        <v>27.55</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[75.4, 65.6, 103.77]</t>
+          <t>[181.21, 81.08, 116.5]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[67.86, 55.34, 88.6]</t>
+          <t>[142.22, 138.52, 135.1]</t>
         </is>
       </c>
     </row>
@@ -7588,31 +7584,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>17.3</v>
+        <v>56.27</v>
       </c>
       <c r="E193" t="n">
-        <v>16.14</v>
+        <v>51.68</v>
       </c>
       <c r="F193" t="n">
-        <v>19.03</v>
+        <v>29</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[65.35, 102.33, 80.27]</t>
+          <t>[79.29, 113.66, 187.8]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[55.34, 88.6, 104.94]</t>
+          <t>[138.52, 135.1, 262.18]</t>
         </is>
       </c>
     </row>
@@ -7624,31 +7620,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>18.92</v>
+        <v>271.65</v>
       </c>
       <c r="E194" t="n">
-        <v>17.03</v>
+        <v>181.76</v>
       </c>
       <c r="F194" t="n">
-        <v>17.13</v>
+        <v>32.3</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[97.66, 76.56, 82.98]</t>
+          <t>[119.22, 198.74, 298.49]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[88.6, 104.94, 96.62]</t>
+          <t>[135.1, 262.18, 764.44]</t>
         </is>
       </c>
     </row>
@@ -7660,31 +7656,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>25.11</v>
+        <v>270.26</v>
       </c>
       <c r="E195" t="n">
-        <v>24.15</v>
+        <v>176.02</v>
       </c>
       <c r="F195" t="n">
-        <v>23.57</v>
+        <v>28.93</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[76.07, 82.16, 74.08]</t>
+          <t>[199.57, 300.54, 67.66]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[104.94, 96.62, 103.21]</t>
+          <t>[262.18, 764.44, 69.2]</t>
         </is>
       </c>
     </row>
@@ -7696,31 +7692,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>16.93</v>
+        <v>266.79</v>
       </c>
       <c r="E196" t="n">
-        <v>14.59</v>
+        <v>155.37</v>
       </c>
       <c r="F196" t="n">
-        <v>17.44</v>
+        <v>22.35</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[84.72, 77.02, 44.57]</t>
+          <t>[302.36, 68.65, 63.61]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[96.62, 103.21, 38.88]</t>
+          <t>[764.44, 69.2, 60.13]</t>
         </is>
       </c>
     </row>
@@ -7732,31 +7728,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>25.05</v>
+        <v>6.86</v>
       </c>
       <c r="E197" t="n">
-        <v>22.14</v>
+        <v>6.41</v>
       </c>
       <c r="F197" t="n">
-        <v>21.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[78.56, 45.57, 177.3]</t>
+          <t>[72.15, 68.41, 101.11]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[103.21, 38.88, 142.22]</t>
+          <t>[69.2, 60.13, 93.1]</t>
         </is>
       </c>
     </row>
@@ -7768,31 +7764,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>40.65</v>
+        <v>7.85</v>
       </c>
       <c r="E198" t="n">
-        <v>35.33</v>
+        <v>7.84</v>
       </c>
       <c r="F198" t="n">
-        <v>30.31</v>
+        <v>10.28</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[47.09, 183.71, 82.23]</t>
+          <t>[68.48, 100.99, 93.07]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[38.88, 142.22, 138.52]</t>
+          <t>[60.13, 93.1, 85.8]</t>
         </is>
       </c>
     </row>
@@ -7804,31 +7800,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>41.49</v>
+        <v>5.32</v>
       </c>
       <c r="E199" t="n">
-        <v>38.34</v>
+        <v>4.39</v>
       </c>
       <c r="F199" t="n">
-        <v>27.55</v>
+        <v>4.9</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[181.21, 81.08, 116.5]</t>
+          <t>[99.94, 91.97, 96.78]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[142.22, 138.52, 135.1]</t>
+          <t>[93.1, 85.8, 96.61]</t>
         </is>
       </c>
     </row>
@@ -7840,31 +7836,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>56.27</v>
+        <v>5.73</v>
       </c>
       <c r="E200" t="n">
-        <v>51.68</v>
+        <v>4.8</v>
       </c>
       <c r="F200" t="n">
-        <v>29</v>
+        <v>4.97</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[79.29, 113.66, 187.8]</t>
+          <t>[91.14, 95.9, 96.65]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[138.52, 135.1, 262.18]</t>
+          <t>[85.8, 96.61, 105.0]</t>
         </is>
       </c>
     </row>
@@ -7876,31 +7872,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>271.65</v>
+        <v>5.04</v>
       </c>
       <c r="E201" t="n">
-        <v>181.76</v>
+        <v>3.7</v>
       </c>
       <c r="F201" t="n">
-        <v>32.3</v>
+        <v>4.31</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[119.22, 198.74, 298.49]</t>
+          <t>[95.76, 96.49, 42.36]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[135.1, 262.18, 764.44]</t>
+          <t>[96.61, 105.0, 44.1]</t>
         </is>
       </c>
     </row>
